--- a/reports/snowbowl_dmr_insights_20251230.xlsx
+++ b/reports/snowbowl_dmr_insights_20251230.xlsx
@@ -908,7 +908,7 @@
         <v>14.67181467181467</v>
       </c>
       <c r="M3" s="5">
-        <v>6731</v>
+        <v>6730</v>
       </c>
       <c r="N3" s="5">
         <v>5550</v>
@@ -917,13 +917,13 @@
         <v>5470</v>
       </c>
       <c r="P3" s="6">
-        <v>21.27927927927928</v>
+        <v>21.26126126126126</v>
       </c>
       <c r="Q3" s="6">
-        <v>23.05301645338208</v>
+        <v>23.03473491773309</v>
       </c>
       <c r="R3" s="5">
-        <v>8666</v>
+        <v>8665</v>
       </c>
       <c r="S3" s="5">
         <v>6150</v>
@@ -932,10 +932,10 @@
         <v>6644</v>
       </c>
       <c r="U3" s="6">
-        <v>40.91056910569106</v>
+        <v>40.89430894308943</v>
       </c>
       <c r="V3" s="6">
-        <v>30.43347381095726</v>
+        <v>30.41842263696568</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="5">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="D5" s="5">
         <v>1850</v>
@@ -1019,13 +1019,13 @@
         <v>1496</v>
       </c>
       <c r="F5" s="6">
-        <v>-7.189189189189189</v>
+        <v>-7.297297297297297</v>
       </c>
       <c r="G5" s="6">
-        <v>14.77272727272727</v>
+        <v>14.63903743315508</v>
       </c>
       <c r="H5" s="5">
-        <v>3420</v>
+        <v>3418</v>
       </c>
       <c r="I5" s="5">
         <v>12550</v>
@@ -1034,13 +1034,13 @@
         <v>3201</v>
       </c>
       <c r="K5" s="6">
-        <v>-72.74900398406375</v>
+        <v>-72.76494023904382</v>
       </c>
       <c r="L5" s="6">
-        <v>6.841611996251172</v>
+        <v>6.779131521399563</v>
       </c>
       <c r="M5" s="5">
-        <v>39686</v>
+        <v>39684</v>
       </c>
       <c r="N5" s="5">
         <v>37250</v>
@@ -1049,13 +1049,13 @@
         <v>33725</v>
       </c>
       <c r="P5" s="6">
-        <v>6.539597315436242</v>
+        <v>6.534228187919464</v>
       </c>
       <c r="Q5" s="6">
-        <v>17.67531504818384</v>
+        <v>17.66938472942921</v>
       </c>
       <c r="R5" s="5">
-        <v>51655</v>
+        <v>51647</v>
       </c>
       <c r="S5" s="5">
         <v>42150</v>
@@ -1064,10 +1064,10 @@
         <v>43591</v>
       </c>
       <c r="U5" s="6">
-        <v>22.55041518386714</v>
+        <v>22.53143534994069</v>
       </c>
       <c r="V5" s="6">
-        <v>18.49923149273933</v>
+        <v>18.48087908054415</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1121,7 +1121,7 @@
         <v>70.00284333238555</v>
       </c>
       <c r="R6" s="5">
-        <v>9355</v>
+        <v>9349</v>
       </c>
       <c r="S6" s="5">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="6">
-        <v>47.11432615191068</v>
+        <v>47.01997169366253</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1170,7 +1170,7 @@
         <v>29</v>
       </c>
       <c r="C8" s="5">
-        <v>24126.56</v>
+        <v>927.9400000000001</v>
       </c>
       <c r="D8" s="5">
         <v>911.72</v>
@@ -1179,13 +1179,13 @@
         <v>897.27</v>
       </c>
       <c r="F8" s="6">
-        <v>2546.268591234151</v>
+        <v>1.779054973018035</v>
       </c>
       <c r="G8" s="6">
-        <v>2588.885173916436</v>
+        <v>3.418146154446273</v>
       </c>
       <c r="H8" s="5">
-        <v>48253.12</v>
+        <v>1855.88</v>
       </c>
       <c r="I8" s="5">
         <v>1823.44</v>
@@ -1194,13 +1194,13 @@
         <v>1794.54</v>
       </c>
       <c r="K8" s="6">
-        <v>2546.268591234151</v>
+        <v>1.779054973018035</v>
       </c>
       <c r="L8" s="6">
-        <v>2588.885173916436</v>
+        <v>3.418146154446273</v>
       </c>
       <c r="M8" s="5">
-        <v>723796.8</v>
+        <v>27838.2</v>
       </c>
       <c r="N8" s="5">
         <v>27351.6</v>
@@ -1209,13 +1209,13 @@
         <v>26918.1</v>
       </c>
       <c r="P8" s="6">
-        <v>2546.268591234151</v>
+        <v>1.77905497301804</v>
       </c>
       <c r="Q8" s="6">
-        <v>2588.885173916436</v>
+        <v>3.418146154446273</v>
       </c>
       <c r="R8" s="5">
-        <v>1447593.6</v>
+        <v>55676.4</v>
       </c>
       <c r="S8" s="5">
         <v>54703.2</v>
@@ -1224,10 +1224,10 @@
         <v>53836.2</v>
       </c>
       <c r="U8" s="6">
-        <v>2546.268591234151</v>
+        <v>1.77905497301804</v>
       </c>
       <c r="V8" s="6">
-        <v>2588.885173916436</v>
+        <v>3.418146154446273</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1238,7 +1238,7 @@
         <v>31</v>
       </c>
       <c r="C9" s="5">
-        <v>7973.466361111111</v>
+        <v>3641.276361111111</v>
       </c>
       <c r="D9" s="5">
         <v>5715.51</v>
@@ -1247,13 +1247,13 @@
         <v>6123.31</v>
       </c>
       <c r="F9" s="6">
-        <v>39.50577220774893</v>
+        <v>-36.29131326668818</v>
       </c>
       <c r="G9" s="6">
-        <v>30.21497133267972</v>
+        <v>-40.53418231134614</v>
       </c>
       <c r="H9" s="5">
-        <v>15996.97748611111</v>
+        <v>7332.597486111112</v>
       </c>
       <c r="I9" s="5">
         <v>11431.02</v>
@@ -1262,13 +1262,13 @@
         <v>12364.61</v>
       </c>
       <c r="K9" s="6">
-        <v>39.94357009357967</v>
+        <v>-35.85351538085742</v>
       </c>
       <c r="L9" s="6">
-        <v>29.37712945342482</v>
+        <v>-40.69689633469142</v>
       </c>
       <c r="M9" s="5">
-        <v>287715.5312499999</v>
+        <v>157749.8312499999</v>
       </c>
       <c r="N9" s="5">
         <v>137180.71</v>
@@ -1277,13 +1277,13 @@
         <v>142682</v>
       </c>
       <c r="P9" s="6">
-        <v>109.7346859117437</v>
+        <v>14.99417902852372</v>
       </c>
       <c r="Q9" s="6">
-        <v>101.6480924363269</v>
+        <v>10.56042896090602</v>
       </c>
       <c r="R9" s="5">
-        <v>483264.3773888889</v>
+        <v>223332.9773888889</v>
       </c>
       <c r="S9" s="5">
         <v>165862.09</v>
@@ -1292,10 +1292,10 @@
         <v>207923.75</v>
       </c>
       <c r="U9" s="6">
-        <v>191.3651801860744</v>
+        <v>34.6498029711846</v>
       </c>
       <c r="V9" s="6">
-        <v>132.4238464287455</v>
+        <v>7.410999171036911</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1306,7 +1306,7 @@
         <v>33</v>
       </c>
       <c r="C10" s="5">
-        <v>6632.707944444444</v>
+        <v>999.1479444444445</v>
       </c>
       <c r="D10" s="5">
         <v>1191.77</v>
@@ -1315,13 +1315,13 @@
         <v>1151.86</v>
       </c>
       <c r="F10" s="6">
-        <v>456.5426168173761</v>
+        <v>-16.16268705837162</v>
       </c>
       <c r="G10" s="6">
-        <v>475.8258767944407</v>
+        <v>-13.25786602152652</v>
       </c>
       <c r="H10" s="5">
-        <v>13206.37361111111</v>
+        <v>1939.253611111111</v>
       </c>
       <c r="I10" s="5">
         <v>2347.04</v>
@@ -1330,13 +1330,13 @@
         <v>2297.45</v>
       </c>
       <c r="K10" s="6">
-        <v>462.6820851417577</v>
+        <v>-17.37449676566606</v>
       </c>
       <c r="L10" s="6">
-        <v>474.8274657168213</v>
+        <v>-15.59104175885824</v>
       </c>
       <c r="M10" s="5">
-        <v>205264.5671916667</v>
+        <v>36257.76719166668</v>
       </c>
       <c r="N10" s="5">
         <v>36567.8</v>
@@ -1345,13 +1345,13 @@
         <v>39167.1</v>
       </c>
       <c r="P10" s="6">
-        <v>461.3259949782779</v>
+        <v>-0.8478300809272705</v>
       </c>
       <c r="Q10" s="6">
-        <v>424.0739477563228</v>
+        <v>-7.428001583812225</v>
       </c>
       <c r="R10" s="5">
-        <v>411089.6903055555</v>
+        <v>73076.09030555554</v>
       </c>
       <c r="S10" s="5">
         <v>72037.7</v>
@@ -1360,10 +1360,10 @@
         <v>77691.28</v>
       </c>
       <c r="U10" s="6">
-        <v>470.6590997568711</v>
+        <v>1.441453996387367</v>
       </c>
       <c r="V10" s="6">
-        <v>429.1323431735912</v>
+        <v>-5.940421749319177</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1374,7 +1374,7 @@
         <v>35</v>
       </c>
       <c r="C11" s="5">
-        <v>6517.657180555556</v>
+        <v>2134.097180555556</v>
       </c>
       <c r="D11" s="5">
         <v>2522.72</v>
@@ -1383,13 +1383,13 @@
         <v>1791.97</v>
       </c>
       <c r="F11" s="6">
-        <v>158.3583267487298</v>
+        <v>-15.40491292907829</v>
       </c>
       <c r="G11" s="6">
-        <v>263.714636994791</v>
+        <v>19.09223818231086</v>
       </c>
       <c r="H11" s="5">
-        <v>14101.32141666667</v>
+        <v>5334.201416666667</v>
       </c>
       <c r="I11" s="5">
         <v>5045.44</v>
@@ -1398,13 +1398,13 @@
         <v>3313.77</v>
       </c>
       <c r="K11" s="6">
-        <v>179.4864554264181</v>
+        <v>5.723215748609976</v>
       </c>
       <c r="L11" s="6">
-        <v>325.5371198564374</v>
+        <v>60.97078000786617</v>
       </c>
       <c r="M11" s="5">
-        <v>208915.7474027778</v>
+        <v>77408.94740277782</v>
       </c>
       <c r="N11" s="5">
         <v>62941.68</v>
@@ -1413,13 +1413,13 @@
         <v>60026.36</v>
       </c>
       <c r="P11" s="6">
-        <v>231.9195601432593</v>
+        <v>22.98519423500901</v>
       </c>
       <c r="Q11" s="6">
-        <v>248.040006761659</v>
+        <v>28.95825667719618</v>
       </c>
       <c r="R11" s="5">
-        <v>387272.1669305557</v>
+        <v>154943.4869305556</v>
       </c>
       <c r="S11" s="5">
         <v>146343.4</v>
@@ -1428,10 +1428,10 @@
         <v>130415.67</v>
       </c>
       <c r="U11" s="6">
-        <v>164.6324787660774</v>
+        <v>5.876648301567164</v>
       </c>
       <c r="V11" s="6">
-        <v>196.9521737154406</v>
+        <v>18.80741549735215</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1466,13 +1466,13 @@
         <v>1205.24</v>
       </c>
       <c r="K12" s="6">
-        <v>-31.98859833095562</v>
+        <v>-31.98859833095563</v>
       </c>
       <c r="L12" s="6">
-        <v>-2.958873566905974</v>
+        <v>-2.958873566905993</v>
       </c>
       <c r="M12" s="5">
-        <v>23188.70852777778</v>
+        <v>23188.70852777777</v>
       </c>
       <c r="N12" s="5">
         <v>20640.32</v>
@@ -1481,10 +1481,10 @@
         <v>14293.89</v>
       </c>
       <c r="P12" s="6">
-        <v>12.34665222136954</v>
+        <v>12.3466522213695</v>
       </c>
       <c r="Q12" s="6">
-        <v>62.22811654334672</v>
+        <v>62.22811654334667</v>
       </c>
       <c r="R12" s="5">
         <v>39240.32834722223</v>
@@ -1510,7 +1510,7 @@
         <v>39</v>
       </c>
       <c r="C13" s="5">
-        <v>5918.792027777778</v>
+        <v>644.8220277777777</v>
       </c>
       <c r="D13" s="5">
         <v>1436.29</v>
@@ -1519,13 +1519,13 @@
         <v>998.04</v>
       </c>
       <c r="F13" s="6">
-        <v>312.0889254800757</v>
+        <v>-55.10502560222672</v>
       </c>
       <c r="G13" s="6">
-        <v>493.0415642436955</v>
+        <v>-35.39116390347303</v>
       </c>
       <c r="H13" s="5">
-        <v>11745.49661111111</v>
+        <v>1197.556611111111</v>
       </c>
       <c r="I13" s="5">
         <v>2887.02</v>
@@ -1534,13 +1534,13 @@
         <v>1914.8</v>
       </c>
       <c r="K13" s="6">
-        <v>306.838075632005</v>
+        <v>-58.51928247427759</v>
       </c>
       <c r="L13" s="6">
-        <v>513.4059228698095</v>
+        <v>-37.45787491586008</v>
       </c>
       <c r="M13" s="5">
-        <v>181415.9717083333</v>
+        <v>23196.87170833334</v>
       </c>
       <c r="N13" s="5">
         <v>35999.58</v>
@@ -1549,13 +1549,13 @@
         <v>26908.3</v>
       </c>
       <c r="P13" s="6">
-        <v>403.9391340352674</v>
+        <v>-35.56349349538707</v>
       </c>
       <c r="Q13" s="6">
-        <v>574.200791979922</v>
+        <v>-13.79287540151798</v>
       </c>
       <c r="R13" s="5">
-        <v>244549.1518055556</v>
+        <v>38864.32180555556</v>
       </c>
       <c r="S13" s="5">
         <v>56959.82</v>
@@ -1564,10 +1564,10 @@
         <v>44523.11</v>
       </c>
       <c r="U13" s="6">
-        <v>329.3362440498505</v>
+        <v>-31.76888233573146</v>
       </c>
       <c r="V13" s="6">
-        <v>449.263409060049</v>
+        <v>-12.70977744915941</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1623,7 +1623,7 @@
         <v>3.012585252509629</v>
       </c>
       <c r="R14" s="5">
-        <v>42855.13208333333</v>
+        <v>42855.13208333337</v>
       </c>
       <c r="S14" s="5">
         <v>39190</v>
@@ -1632,10 +1632,10 @@
         <v>39407.13</v>
       </c>
       <c r="U14" s="6">
-        <v>9.352212511695154</v>
+        <v>9.352212511695246</v>
       </c>
       <c r="V14" s="6">
-        <v>8.749690940023628</v>
+        <v>8.74969094002372</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1646,7 +1646,7 @@
         <v>43</v>
       </c>
       <c r="C15" s="5">
-        <v>12629.65273611111</v>
+        <v>3965.262736111112</v>
       </c>
       <c r="D15" s="5">
         <v>3197.82</v>
@@ -1655,13 +1655,13 @@
         <v>2306.31</v>
       </c>
       <c r="F15" s="6">
-        <v>294.9457047648432</v>
+        <v>23.9989347777896</v>
       </c>
       <c r="G15" s="6">
-        <v>447.6129720684172</v>
+        <v>71.93103859026375</v>
       </c>
       <c r="H15" s="5">
-        <v>24683.56991666666</v>
+        <v>7354.789916666666</v>
       </c>
       <c r="I15" s="5">
         <v>6395.64</v>
@@ -1670,13 +1670,13 @@
         <v>5478.58</v>
       </c>
       <c r="K15" s="6">
-        <v>285.9437040963322</v>
+        <v>14.99693410927859</v>
       </c>
       <c r="L15" s="6">
-        <v>350.5468555112213</v>
+        <v>34.24628127483154</v>
       </c>
       <c r="M15" s="5">
-        <v>361457.8707916667</v>
+        <v>101526.1707916667</v>
       </c>
       <c r="N15" s="5">
         <v>75973.5</v>
@@ -1685,13 +1685,13 @@
         <v>82627.09</v>
       </c>
       <c r="P15" s="6">
-        <v>375.7683544810582</v>
+        <v>33.63366277934637</v>
       </c>
       <c r="Q15" s="6">
-        <v>337.4568568149583</v>
+        <v>22.87274160528552</v>
       </c>
       <c r="R15" s="5">
-        <v>686615.2885416665</v>
+        <v>166751.8885416667</v>
       </c>
       <c r="S15" s="5">
         <v>121145.25</v>
@@ -1700,10 +1700,10 @@
         <v>131186.92</v>
       </c>
       <c r="U15" s="6">
-        <v>466.7702931329676</v>
+        <v>37.64624576008282</v>
       </c>
       <c r="V15" s="6">
-        <v>423.3870027146505</v>
+        <v>27.11014828434627</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1714,7 +1714,7 @@
         <v>45</v>
       </c>
       <c r="C16" s="5">
-        <v>15596.48590277778</v>
+        <v>2685.515902777777</v>
       </c>
       <c r="D16" s="5">
         <v>2761.07</v>
@@ -1723,13 +1723,13 @@
         <v>2402.35</v>
       </c>
       <c r="F16" s="6">
-        <v>464.8710790663684</v>
+        <v>-2.736406437439939</v>
       </c>
       <c r="G16" s="6">
-        <v>549.2178867682802</v>
+        <v>11.78703780788716</v>
       </c>
       <c r="H16" s="5">
-        <v>31163.42252777778</v>
+        <v>5341.482527777777</v>
       </c>
       <c r="I16" s="5">
         <v>5522.14</v>
@@ -1738,13 +1738,13 @@
         <v>4933.8</v>
       </c>
       <c r="K16" s="6">
-        <v>464.3359735134889</v>
+        <v>-3.271511990319388</v>
       </c>
       <c r="L16" s="6">
-        <v>531.63124828282</v>
+        <v>8.263053382337691</v>
       </c>
       <c r="M16" s="5">
-        <v>453417.5708194444</v>
+        <v>66088.47081944444</v>
       </c>
       <c r="N16" s="5">
         <v>55376.92</v>
@@ -1753,13 +1753,13 @@
         <v>56109.52</v>
       </c>
       <c r="P16" s="6">
-        <v>718.7843795202848</v>
+        <v>19.34298769134224</v>
       </c>
       <c r="Q16" s="6">
-        <v>708.0938329528473</v>
+        <v>17.78477309990256</v>
       </c>
       <c r="R16" s="5">
-        <v>877206.6742083334</v>
+        <v>102548.4742083334</v>
       </c>
       <c r="S16" s="5">
         <v>86271.89</v>
@@ -1768,10 +1768,10 @@
         <v>87320.69</v>
       </c>
       <c r="U16" s="6">
-        <v>916.7931573173294</v>
+        <v>18.86661368880804</v>
       </c>
       <c r="V16" s="6">
-        <v>904.5805572635001</v>
+        <v>17.43891878125724</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1782,7 +1782,7 @@
         <v>47</v>
       </c>
       <c r="C17" s="5">
-        <v>13692.78368055555</v>
+        <v>1055.803680555556</v>
       </c>
       <c r="D17" s="5">
         <v>6723.41</v>
@@ -1791,13 +1791,13 @@
         <v>8083.35</v>
       </c>
       <c r="F17" s="6">
-        <v>103.6583174394475</v>
+        <v>-84.29660424463843</v>
       </c>
       <c r="G17" s="6">
-        <v>69.39491275963002</v>
+        <v>-86.93853809923415</v>
       </c>
       <c r="H17" s="5">
-        <v>27657.383</v>
+        <v>2383.423</v>
       </c>
       <c r="I17" s="5">
         <v>13349.98</v>
@@ -1806,13 +1806,13 @@
         <v>14127.24</v>
       </c>
       <c r="K17" s="6">
-        <v>107.1717186093163</v>
+        <v>-82.14661744811602</v>
       </c>
       <c r="L17" s="6">
-        <v>95.77343486767407</v>
+        <v>-83.12888433975779</v>
       </c>
       <c r="M17" s="5">
-        <v>511420.0782083329</v>
+        <v>132310.6782083331</v>
       </c>
       <c r="N17" s="5">
         <v>158574.5</v>
@@ -1821,13 +1821,13 @@
         <v>253618.91</v>
       </c>
       <c r="P17" s="6">
-        <v>222.5109196045599</v>
+        <v>-16.56244969504361</v>
       </c>
       <c r="Q17" s="6">
-        <v>101.6490324827644</v>
+        <v>-47.83090968716289</v>
       </c>
       <c r="R17" s="5">
-        <v>939566.2384861106</v>
+        <v>181347.4384861107</v>
       </c>
       <c r="S17" s="5">
         <v>204095.93</v>
@@ -1836,10 +1836,10 @@
         <v>297231.74</v>
       </c>
       <c r="U17" s="6">
-        <v>360.3552057535447</v>
+        <v>-11.14597998788572</v>
       </c>
       <c r="V17" s="6">
-        <v>216.1056213196177</v>
+        <v>-38.98786230363193</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -1859,13 +1859,13 @@
         <v>2917.66</v>
       </c>
       <c r="F18" s="6">
-        <v>-0.7801274343370589</v>
+        <v>-0.7801274343370276</v>
       </c>
       <c r="G18" s="6">
-        <v>-1.108971839685855</v>
+        <v>-1.108971839685823</v>
       </c>
       <c r="H18" s="5">
-        <v>5197.864402777777</v>
+        <v>5197.864402777779</v>
       </c>
       <c r="I18" s="5">
         <v>5928.38</v>
@@ -1874,13 +1874,13 @@
         <v>5757.55</v>
       </c>
       <c r="K18" s="6">
-        <v>-12.32234771087924</v>
+        <v>-12.32234771087921</v>
       </c>
       <c r="L18" s="6">
-        <v>-9.720898597879705</v>
+        <v>-9.720898597879673</v>
       </c>
       <c r="M18" s="5">
-        <v>59810.40005555559</v>
+        <v>59810.40005555555</v>
       </c>
       <c r="N18" s="5">
         <v>60156.28</v>
@@ -1889,13 +1889,13 @@
         <v>67142.56</v>
       </c>
       <c r="P18" s="6">
-        <v>-0.5749689715594257</v>
+        <v>-0.5749689715594861</v>
       </c>
       <c r="Q18" s="6">
-        <v>-10.92028654320658</v>
+        <v>-10.92028654320664</v>
       </c>
       <c r="R18" s="5">
-        <v>80603.1825277777</v>
+        <v>80603.18252777768</v>
       </c>
       <c r="S18" s="5">
         <v>86086.75</v>
@@ -1904,10 +1904,10 @@
         <v>91110.87</v>
       </c>
       <c r="U18" s="6">
-        <v>-6.369815880170067</v>
+        <v>-6.369815880170083</v>
       </c>
       <c r="V18" s="6">
-        <v>-11.53285823329566</v>
+        <v>-11.53285823329567</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -1948,7 +1948,7 @@
         <v>5.517445390711377</v>
       </c>
       <c r="M19" s="5">
-        <v>10858.30918055555</v>
+        <v>10858.30918055556</v>
       </c>
       <c r="N19" s="5">
         <v>10735.55</v>
@@ -1957,10 +1957,10 @@
         <v>10368.82</v>
       </c>
       <c r="P19" s="6">
-        <v>1.143482919417774</v>
+        <v>1.143482919417808</v>
       </c>
       <c r="Q19" s="6">
-        <v>4.720779997681071</v>
+        <v>4.720779997681106</v>
       </c>
       <c r="R19" s="5">
         <v>15592.65661111111</v>
@@ -1972,10 +1972,10 @@
         <v>18845.14</v>
       </c>
       <c r="U19" s="6">
-        <v>-16.89501129315174</v>
+        <v>-16.89501129315173</v>
       </c>
       <c r="V19" s="6">
-        <v>-17.25900358866471</v>
+        <v>-17.25900358866469</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -2054,7 +2054,7 @@
         <v>55</v>
       </c>
       <c r="C21" s="5">
-        <v>5197.470125000001</v>
+        <v>919.3681250000002</v>
       </c>
       <c r="D21" s="5">
         <v>615.13</v>
@@ -2063,13 +2063,13 @@
         <v>289.75</v>
       </c>
       <c r="F21" s="6">
-        <v>744.9384886121634</v>
+        <v>49.45915903955265</v>
       </c>
       <c r="G21" s="6">
-        <v>1693.777437446074</v>
+        <v>217.2970232959449</v>
       </c>
       <c r="H21" s="5">
-        <v>10266.06580555556</v>
+        <v>1535.903805555556</v>
       </c>
       <c r="I21" s="5">
         <v>1230.26</v>
@@ -2078,13 +2078,13 @@
         <v>614.17</v>
       </c>
       <c r="K21" s="6">
-        <v>734.4631058114184</v>
+        <v>24.84383833950187</v>
       </c>
       <c r="L21" s="6">
-        <v>1571.534885382802</v>
+        <v>150.0779597758855</v>
       </c>
       <c r="M21" s="5">
-        <v>154296.8766805556</v>
+        <v>20909.03468055556</v>
       </c>
       <c r="N21" s="5">
         <v>16008.71</v>
@@ -2093,13 +2093,13 @@
         <v>20933.74</v>
       </c>
       <c r="P21" s="6">
-        <v>863.8307938650621</v>
+        <v>30.61036573562493</v>
       </c>
       <c r="Q21" s="6">
-        <v>637.0726715845118</v>
+        <v>-0.1180167492499742</v>
       </c>
       <c r="R21" s="5">
-        <v>301794.3686944445</v>
+        <v>34844.72669444444</v>
       </c>
       <c r="S21" s="5">
         <v>29891.72</v>
@@ -2108,10 +2108,10 @@
         <v>37090.34</v>
       </c>
       <c r="U21" s="6">
-        <v>909.625303242652</v>
+        <v>16.56982834860102</v>
       </c>
       <c r="V21" s="6">
-        <v>713.6737724551581</v>
+        <v>-6.054442492453709</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2167,7 +2167,7 @@
         <v>-54.90375891711281</v>
       </c>
       <c r="R22" s="5">
-        <v>6155.694222222219</v>
+        <v>6155.69422222222</v>
       </c>
       <c r="S22" s="5">
         <v>10911.62</v>
@@ -2176,10 +2176,10 @@
         <v>10545.58</v>
       </c>
       <c r="U22" s="6">
-        <v>-43.58588163607038</v>
+        <v>-43.58588163607036</v>
       </c>
       <c r="V22" s="6">
-        <v>-41.62773197659855</v>
+        <v>-41.62773197659854</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2190,7 +2190,7 @@
         <v>59</v>
       </c>
       <c r="C23" s="5">
-        <v>24678.82263888889</v>
+        <v>1171.972638888889</v>
       </c>
       <c r="D23" s="5">
         <v>913.71</v>
@@ -2199,13 +2199,13 @@
         <v>928.53</v>
       </c>
       <c r="F23" s="6">
-        <v>2600.946978679109</v>
+        <v>28.26527441845759</v>
       </c>
       <c r="G23" s="6">
-        <v>2557.83794157312</v>
+        <v>26.21806930189536</v>
       </c>
       <c r="H23" s="5">
-        <v>49228.81688888889</v>
+        <v>2215.116888888889</v>
       </c>
       <c r="I23" s="5">
         <v>1827.42</v>
@@ -2214,13 +2214,13 @@
         <v>1857.06</v>
       </c>
       <c r="K23" s="6">
-        <v>2593.897237027552</v>
+        <v>21.21553276690026</v>
       </c>
       <c r="L23" s="6">
-        <v>2550.900718818395</v>
+        <v>19.28084654717073</v>
       </c>
       <c r="M23" s="5">
-        <v>735215.6966805556</v>
+        <v>30010.19668055556</v>
       </c>
       <c r="N23" s="5">
         <v>27411.3</v>
@@ -2229,13 +2229,13 @@
         <v>27855.9</v>
       </c>
       <c r="P23" s="6">
-        <v>2582.162818547663</v>
+        <v>9.481114287011405</v>
       </c>
       <c r="Q23" s="6">
-        <v>2539.353590013446</v>
+        <v>7.733717742221774</v>
       </c>
       <c r="R23" s="5">
-        <v>1470920.473263889</v>
+        <v>60509.47326388889</v>
       </c>
       <c r="S23" s="5">
         <v>54822.6</v>
@@ -2244,10 +2244,10 @@
         <v>55711.8</v>
       </c>
       <c r="U23" s="6">
-        <v>2583.054932206588</v>
+        <v>10.37322794593633</v>
       </c>
       <c r="V23" s="6">
-        <v>2540.231464903106</v>
+        <v>8.61159263188209</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2267,13 +2267,13 @@
         <v>1378.87</v>
       </c>
       <c r="F24" s="6">
-        <v>51.42269198173012</v>
+        <v>51.4226919817301</v>
       </c>
       <c r="G24" s="6">
-        <v>24.24969459694455</v>
+        <v>24.24969459694454</v>
       </c>
       <c r="H24" s="5">
-        <v>3221.641125000001</v>
+        <v>3221.641125</v>
       </c>
       <c r="I24" s="5">
         <v>2262.86</v>
@@ -2282,13 +2282,13 @@
         <v>2434.22</v>
       </c>
       <c r="K24" s="6">
-        <v>42.37032450085292</v>
+        <v>42.3703245008529</v>
       </c>
       <c r="L24" s="6">
-        <v>32.34798518621985</v>
+        <v>32.34798518621983</v>
       </c>
       <c r="M24" s="5">
-        <v>58781.65855555554</v>
+        <v>58781.65855555559</v>
       </c>
       <c r="N24" s="5">
         <v>32605.5</v>
@@ -2297,13 +2297,13 @@
         <v>35386.07</v>
       </c>
       <c r="P24" s="6">
-        <v>80.28142048291099</v>
+        <v>80.28142048291113</v>
       </c>
       <c r="Q24" s="6">
-        <v>66.11524974532504</v>
+        <v>66.11524974532517</v>
       </c>
       <c r="R24" s="5">
-        <v>85541.17161111125</v>
+        <v>85541.1716111112</v>
       </c>
       <c r="S24" s="5">
         <v>58463.68</v>
@@ -2312,10 +2312,10 @@
         <v>61276.33</v>
       </c>
       <c r="U24" s="6">
-        <v>46.31506537240086</v>
+        <v>46.31506537240079</v>
       </c>
       <c r="V24" s="6">
-        <v>39.59904519593658</v>
+        <v>39.5990451959365</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2356,7 +2356,7 @@
         <v>36.57985012462045</v>
       </c>
       <c r="M25" s="5">
-        <v>93166.66872222259</v>
+        <v>93166.6687222224</v>
       </c>
       <c r="N25" s="5">
         <v>62776.99</v>
@@ -2365,10 +2365,10 @@
         <v>61373.62</v>
       </c>
       <c r="P25" s="6">
-        <v>48.4089452556145</v>
+        <v>48.4089452556142</v>
       </c>
       <c r="Q25" s="6">
-        <v>51.80246614461161</v>
+        <v>51.8024661446113</v>
       </c>
       <c r="R25" s="5">
         <v>116235.5070972226</v>
@@ -2380,10 +2380,10 @@
         <v>83909.42999999999</v>
       </c>
       <c r="U25" s="6">
-        <v>39.23276367621601</v>
+        <v>39.23276367621597</v>
       </c>
       <c r="V25" s="6">
-        <v>38.52496328150797</v>
+        <v>38.52496328150794</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2424,7 +2424,7 @@
         <v>18.22905591390228</v>
       </c>
       <c r="M26" s="5">
-        <v>12087.01530555556</v>
+        <v>12087.01530555555</v>
       </c>
       <c r="N26" s="5">
         <v>12112.88</v>
@@ -2433,10 +2433,10 @@
         <v>11707.98</v>
       </c>
       <c r="P26" s="6">
-        <v>-0.2135305100392529</v>
+        <v>-0.2135305100392679</v>
       </c>
       <c r="Q26" s="6">
-        <v>3.237409916617188</v>
+        <v>3.237409916617172</v>
       </c>
       <c r="R26" s="5">
         <v>23520.69309722223</v>
@@ -2462,7 +2462,7 @@
         <v>67</v>
       </c>
       <c r="C27" s="5">
-        <v>875.8101805555555</v>
+        <v>875.8101805555556</v>
       </c>
       <c r="D27" s="5">
         <v>557.02</v>
@@ -2471,13 +2471,13 @@
         <v>564.4299999999999</v>
       </c>
       <c r="F27" s="6">
-        <v>57.23137060707973</v>
+        <v>57.23137060707975</v>
       </c>
       <c r="G27" s="6">
-        <v>55.16719177852977</v>
+        <v>55.16719177852978</v>
       </c>
       <c r="H27" s="5">
-        <v>1446.017472222223</v>
+        <v>1446.017472222222</v>
       </c>
       <c r="I27" s="5">
         <v>1114.04</v>
@@ -2486,13 +2486,13 @@
         <v>1183.67</v>
       </c>
       <c r="K27" s="6">
-        <v>29.79942122564922</v>
+        <v>29.7994212256492</v>
       </c>
       <c r="L27" s="6">
-        <v>22.16390313366246</v>
+        <v>22.16390313366244</v>
       </c>
       <c r="M27" s="5">
-        <v>18844.42941666666</v>
+        <v>18844.42941666667</v>
       </c>
       <c r="N27" s="5">
         <v>11019.69</v>
@@ -2501,10 +2501,10 @@
         <v>3857.5</v>
       </c>
       <c r="P27" s="6">
-        <v>71.00689235964587</v>
+        <v>71.00689235964595</v>
       </c>
       <c r="Q27" s="6">
-        <v>388.514048390581</v>
+        <v>388.5140483905812</v>
       </c>
       <c r="R27" s="5">
         <v>19310.53151388889</v>
@@ -2666,7 +2666,7 @@
         <v>72</v>
       </c>
       <c r="C30" s="5">
-        <v>4790.374222222222</v>
+        <v>406.8142222222223</v>
       </c>
       <c r="D30" s="5">
         <v>644.84</v>
@@ -2675,13 +2675,13 @@
         <v>662.9</v>
       </c>
       <c r="F30" s="6">
-        <v>642.8779576673627</v>
+        <v>-36.91237791975959</v>
       </c>
       <c r="G30" s="6">
-        <v>622.6390439315467</v>
+        <v>-38.63113256566265</v>
       </c>
       <c r="H30" s="5">
-        <v>9793.343652777778</v>
+        <v>1026.223652777778</v>
       </c>
       <c r="I30" s="5">
         <v>1075.28</v>
@@ -2690,13 +2690,13 @@
         <v>1231.41</v>
       </c>
       <c r="K30" s="6">
-        <v>810.7714876848613</v>
+        <v>-4.562192844861062</v>
       </c>
       <c r="L30" s="6">
-        <v>695.2951212656855</v>
+        <v>-16.66271568545181</v>
       </c>
       <c r="M30" s="5">
-        <v>126862.2541111111</v>
+        <v>17273.25411111111</v>
       </c>
       <c r="N30" s="5">
         <v>17415.6</v>
@@ -2705,13 +2705,13 @@
         <v>16911.71</v>
       </c>
       <c r="P30" s="6">
-        <v>628.4403299978818</v>
+        <v>-0.8173470273139752</v>
       </c>
       <c r="Q30" s="6">
-        <v>650.1444508634025</v>
+        <v>2.137832963734045</v>
       </c>
       <c r="R30" s="5">
-        <v>139083.7060833333</v>
+        <v>29494.70608333333</v>
       </c>
       <c r="S30" s="5">
         <v>33176.4</v>
@@ -2720,10 +2720,10 @@
         <v>32967.58</v>
       </c>
       <c r="U30" s="6">
-        <v>319.2248287437254</v>
+        <v>-11.09732797008315</v>
       </c>
       <c r="V30" s="6">
-        <v>321.880241386639</v>
+        <v>-10.53420941624064</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -2764,7 +2764,7 @@
         <v>32.91524091603404</v>
       </c>
       <c r="M31" s="5">
-        <v>11897.12680555555</v>
+        <v>11897.12680555556</v>
       </c>
       <c r="N31" s="5">
         <v>9439.76</v>
@@ -2773,13 +2773,13 @@
         <v>11453.63</v>
       </c>
       <c r="P31" s="6">
-        <v>26.03208985774587</v>
+        <v>26.03208985774591</v>
       </c>
       <c r="Q31" s="6">
-        <v>3.872106970065846</v>
+        <v>3.872106970065878</v>
       </c>
       <c r="R31" s="5">
-        <v>21775.108625</v>
+        <v>21775.10862499999</v>
       </c>
       <c r="S31" s="5">
         <v>17934.1</v>
@@ -2788,10 +2788,10 @@
         <v>20435.02</v>
       </c>
       <c r="U31" s="6">
-        <v>21.41734809664272</v>
+        <v>21.41734809664268</v>
       </c>
       <c r="V31" s="6">
-        <v>6.557804323166801</v>
+        <v>6.557804323166764</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -2802,7 +2802,7 @@
         <v>76</v>
       </c>
       <c r="C32" s="5">
-        <v>6500</v>
+        <v>250</v>
       </c>
       <c r="D32" s="5">
         <v>250.06</v>
@@ -2811,13 +2811,13 @@
         <v>208.58</v>
       </c>
       <c r="F32" s="6">
-        <v>2499.376149724066</v>
+        <v>-0.02399424138206921</v>
       </c>
       <c r="G32" s="6">
-        <v>3016.310288618276</v>
+        <v>19.85808802377984</v>
       </c>
       <c r="H32" s="5">
-        <v>13000</v>
+        <v>500</v>
       </c>
       <c r="I32" s="5">
         <v>500.12</v>
@@ -2826,13 +2826,13 @@
         <v>417.16</v>
       </c>
       <c r="K32" s="6">
-        <v>2499.376149724066</v>
+        <v>-0.02399424138206921</v>
       </c>
       <c r="L32" s="6">
-        <v>3016.310288618276</v>
+        <v>19.85808802377984</v>
       </c>
       <c r="M32" s="5">
-        <v>195000</v>
+        <v>7500</v>
       </c>
       <c r="N32" s="5">
         <v>7501.8</v>
@@ -2841,13 +2841,13 @@
         <v>6257.4</v>
       </c>
       <c r="P32" s="6">
-        <v>2499.376149724066</v>
+        <v>-0.02399424138207073</v>
       </c>
       <c r="Q32" s="6">
-        <v>3016.310288618276</v>
+        <v>19.85808802377985</v>
       </c>
       <c r="R32" s="5">
-        <v>390000</v>
+        <v>15000</v>
       </c>
       <c r="S32" s="5">
         <v>15003.6</v>
@@ -2856,10 +2856,10 @@
         <v>12514.8</v>
       </c>
       <c r="U32" s="6">
-        <v>2499.376149724066</v>
+        <v>-0.02399424138207073</v>
       </c>
       <c r="V32" s="6">
-        <v>3016.310288618276</v>
+        <v>19.85808802377985</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -2870,7 +2870,7 @@
         <v>78</v>
       </c>
       <c r="C33" s="5">
-        <v>901.4637916666667</v>
+        <v>901.4637916666668</v>
       </c>
       <c r="D33" s="5">
         <v>859.02</v>
@@ -2879,10 +2879,10 @@
         <v>686.46</v>
       </c>
       <c r="F33" s="6">
-        <v>4.940955002987905</v>
+        <v>4.940955002987918</v>
       </c>
       <c r="G33" s="6">
-        <v>31.32065840204333</v>
+        <v>31.32065840204334</v>
       </c>
       <c r="H33" s="5">
         <v>1993.520236111111</v>
@@ -2894,13 +2894,13 @@
         <v>1585</v>
       </c>
       <c r="K33" s="6">
-        <v>16.03456474302759</v>
+        <v>16.03456474302761</v>
       </c>
       <c r="L33" s="6">
-        <v>25.77414738871364</v>
+        <v>25.77414738871366</v>
       </c>
       <c r="M33" s="5">
-        <v>18223.75451388889</v>
+        <v>18223.75451388887</v>
       </c>
       <c r="N33" s="5">
         <v>16335.83</v>
@@ -2909,10 +2909,10 @@
         <v>16766.6</v>
       </c>
       <c r="P33" s="6">
-        <v>11.55695495049158</v>
+        <v>11.55695495049149</v>
       </c>
       <c r="Q33" s="6">
-        <v>8.690816944931534</v>
+        <v>8.690816944931449</v>
       </c>
       <c r="R33" s="5">
         <v>20785.16422222223</v>
@@ -2924,10 +2924,10 @@
         <v>22290.43</v>
       </c>
       <c r="U33" s="6">
-        <v>-0.5431719983165028</v>
+        <v>-0.5431719983165201</v>
       </c>
       <c r="V33" s="6">
-        <v>-6.752968775289537</v>
+        <v>-6.752968775289552</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -2938,7 +2938,7 @@
         <v>80</v>
       </c>
       <c r="C34" s="5">
-        <v>5205.323333333334</v>
+        <v>753.2633333333334</v>
       </c>
       <c r="D34" s="5">
         <v>615.88</v>
@@ -2947,13 +2947,13 @@
         <v>892.6</v>
       </c>
       <c r="F34" s="6">
-        <v>745.1846680089195</v>
+        <v>22.30683466476155</v>
       </c>
       <c r="G34" s="6">
-        <v>483.1641646127418</v>
+        <v>-15.61020240495929</v>
       </c>
       <c r="H34" s="5">
-        <v>10661.26533333333</v>
+        <v>1757.145333333333</v>
       </c>
       <c r="I34" s="5">
         <v>1056.65</v>
@@ -2962,13 +2962,13 @@
         <v>1777.38</v>
       </c>
       <c r="K34" s="6">
-        <v>908.9684695342198</v>
+        <v>66.29397940030599</v>
       </c>
       <c r="L34" s="6">
-        <v>499.8303870491023</v>
+        <v>-1.138454729245672</v>
       </c>
       <c r="M34" s="5">
-        <v>155169.2583611111</v>
+        <v>21607.45836111112</v>
       </c>
       <c r="N34" s="5">
         <v>13989.38</v>
@@ -2977,13 +2977,13 @@
         <v>13358.72</v>
       </c>
       <c r="P34" s="6">
-        <v>1009.19324774301</v>
+        <v>54.45615431928447</v>
       </c>
       <c r="Q34" s="6">
-        <v>1061.557831596973</v>
+        <v>61.74796957426397</v>
       </c>
       <c r="R34" s="5">
-        <v>299273.635125</v>
+        <v>32150.03512499999</v>
       </c>
       <c r="S34" s="5">
         <v>24104.66</v>
@@ -2992,10 +2992,10 @@
         <v>22226.82</v>
       </c>
       <c r="U34" s="6">
-        <v>1141.559246739012</v>
+        <v>33.37684549377586</v>
       </c>
       <c r="V34" s="6">
-        <v>1246.452776982942</v>
+        <v>44.64523096421347</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3036,7 +3036,7 @@
         <v>-25.81019209274689</v>
       </c>
       <c r="M35" s="5">
-        <v>29571.48324999999</v>
+        <v>29571.48325</v>
       </c>
       <c r="N35" s="5">
         <v>25312.5</v>
@@ -3045,13 +3045,13 @@
         <v>24267.58</v>
       </c>
       <c r="P35" s="6">
-        <v>16.82561283950614</v>
+        <v>16.82561283950616</v>
       </c>
       <c r="Q35" s="6">
-        <v>21.85592156284223</v>
+        <v>21.85592156284226</v>
       </c>
       <c r="R35" s="5">
-        <v>43101.32484722223</v>
+        <v>43101.32484722228</v>
       </c>
       <c r="S35" s="5">
         <v>35424.31</v>
@@ -3060,10 +3060,10 @@
         <v>37150.54</v>
       </c>
       <c r="U35" s="6">
-        <v>21.67160022939679</v>
+        <v>21.67160022939693</v>
       </c>
       <c r="V35" s="6">
-        <v>16.0180305514327</v>
+        <v>16.01803055143284</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3074,7 +3074,7 @@
         <v>84</v>
       </c>
       <c r="C36" s="5">
-        <v>6323.932652777778</v>
+        <v>1032.832652777778</v>
       </c>
       <c r="D36" s="5">
         <v>589.33</v>
@@ -3083,13 +3083,13 @@
         <v>765.8</v>
       </c>
       <c r="F36" s="6">
-        <v>973.0715647901477</v>
+        <v>75.25540067157239</v>
       </c>
       <c r="G36" s="6">
-        <v>725.7942873828385</v>
+        <v>34.86976400858941</v>
       </c>
       <c r="H36" s="5">
-        <v>12489.96413888889</v>
+        <v>1907.764138888889</v>
       </c>
       <c r="I36" s="5">
         <v>1227.03</v>
@@ -3098,13 +3098,13 @@
         <v>1634.03</v>
       </c>
       <c r="K36" s="6">
-        <v>917.9021001025964</v>
+        <v>55.47819848649903</v>
       </c>
       <c r="L36" s="6">
-        <v>664.3656566212914</v>
+        <v>16.75208771496784</v>
       </c>
       <c r="M36" s="5">
-        <v>182510.0767638889</v>
+        <v>23777.07676388889</v>
       </c>
       <c r="N36" s="5">
         <v>21432.21</v>
@@ -3113,13 +3113,13 @@
         <v>21147.37</v>
       </c>
       <c r="P36" s="6">
-        <v>751.5690951324615</v>
+        <v>10.94085380783824</v>
       </c>
       <c r="Q36" s="6">
-        <v>763.0391238432435</v>
+        <v>12.43514802970245</v>
       </c>
       <c r="R36" s="5">
-        <v>364200.6233472222</v>
+        <v>46734.62334722223</v>
       </c>
       <c r="S36" s="5">
         <v>42652.82</v>
@@ -3128,10 +3128,10 @@
         <v>42861.37</v>
       </c>
       <c r="U36" s="6">
-        <v>753.8723192211493</v>
+        <v>9.569832304692236</v>
       </c>
       <c r="V36" s="6">
-        <v>749.7176439932326</v>
+        <v>9.036699823692587</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3172,7 +3172,7 @@
         <v>-66.55584302733922</v>
       </c>
       <c r="M37" s="5">
-        <v>9582.76023888889</v>
+        <v>9582.760238888892</v>
       </c>
       <c r="N37" s="5">
         <v>9578.120000000001</v>
@@ -3181,10 +3181,10 @@
         <v>6192.13</v>
       </c>
       <c r="P37" s="6">
-        <v>0.04844623881188734</v>
+        <v>0.04844623881190633</v>
       </c>
       <c r="Q37" s="6">
-        <v>54.75709067621142</v>
+        <v>54.75709067621144</v>
       </c>
       <c r="R37" s="5">
         <v>20665.16781666666</v>
@@ -3196,10 +3196,10 @@
         <v>17088.25</v>
       </c>
       <c r="U37" s="6">
-        <v>15.85406608122478</v>
+        <v>15.85406608122476</v>
       </c>
       <c r="V37" s="6">
-        <v>20.93203117151646</v>
+        <v>20.93203117151643</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3240,7 +3240,7 @@
         <v>-100</v>
       </c>
       <c r="M38" s="5">
-        <v>734.7059166666667</v>
+        <v>734.7059166666668</v>
       </c>
       <c r="N38" s="5">
         <v>0</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="Q38" s="6">
-        <v>-39.39420123679818</v>
+        <v>-39.39420123679817</v>
       </c>
       <c r="R38" s="5">
         <v>3038.395875</v>
@@ -3308,7 +3308,7 @@
         <v>68.698265431129</v>
       </c>
       <c r="M39" s="5">
-        <v>30796.1842638889</v>
+        <v>30796.18426388892</v>
       </c>
       <c r="N39" s="5">
         <v>17937.63</v>
@@ -3317,13 +3317,13 @@
         <v>19858.43</v>
       </c>
       <c r="P39" s="6">
-        <v>71.68480041058322</v>
+        <v>71.68480041058336</v>
       </c>
       <c r="Q39" s="6">
-        <v>55.07864551169905</v>
+        <v>55.07864551169919</v>
       </c>
       <c r="R39" s="5">
-        <v>41107.83520277778</v>
+        <v>41107.83520277781</v>
       </c>
       <c r="S39" s="5">
         <v>22147.23</v>
@@ -3332,10 +3332,10 @@
         <v>28885.15</v>
       </c>
       <c r="U39" s="6">
-        <v>85.61163270882084</v>
+        <v>85.61163270882098</v>
       </c>
       <c r="V39" s="6">
-        <v>42.31477144061145</v>
+        <v>42.31477144061155</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -3414,7 +3414,7 @@
         <v>93</v>
       </c>
       <c r="C41" s="5">
-        <v>8296.319166666666</v>
+        <v>522.3491666666666</v>
       </c>
       <c r="D41" s="5">
         <v>587.05</v>
@@ -3423,13 +3423,13 @@
         <v>569.6900000000001</v>
       </c>
       <c r="F41" s="6">
-        <v>1313.221900462766</v>
+        <v>-11.02134968628453</v>
       </c>
       <c r="G41" s="6">
-        <v>1356.286606165926</v>
+        <v>-8.30992879168204</v>
       </c>
       <c r="H41" s="5">
-        <v>16567.21694444444</v>
+        <v>1019.276944444444</v>
       </c>
       <c r="I41" s="5">
         <v>1174.1</v>
@@ -3438,13 +3438,13 @@
         <v>1182.97</v>
       </c>
       <c r="K41" s="6">
-        <v>1311.056719567707</v>
+        <v>-13.18653058134362</v>
       </c>
       <c r="L41" s="6">
-        <v>1300.476507810379</v>
+        <v>-13.8374646487701</v>
       </c>
       <c r="M41" s="5">
-        <v>250317.2497361111</v>
+        <v>17098.14973611111</v>
       </c>
       <c r="N41" s="5">
         <v>15403.5</v>
@@ -3453,13 +3453,13 @@
         <v>9707.790000000001</v>
       </c>
       <c r="P41" s="6">
-        <v>1525.067353108781</v>
+        <v>11.0017186750486</v>
       </c>
       <c r="Q41" s="6">
-        <v>2478.519413132248</v>
+        <v>76.12813767202535</v>
       </c>
       <c r="R41" s="5">
-        <v>501662.6179027777</v>
+        <v>35224.41790277777</v>
       </c>
       <c r="S41" s="5">
         <v>32199</v>
@@ -3468,10 +3468,10 @@
         <v>15730.31</v>
       </c>
       <c r="U41" s="6">
-        <v>1458.006825997011</v>
+        <v>9.395999573830776</v>
       </c>
       <c r="V41" s="6">
-        <v>3089.146417983993</v>
+        <v>123.927042142067</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -3550,7 +3550,7 @@
         <v>97</v>
       </c>
       <c r="C43" s="5">
-        <v>15616.36240277778</v>
+        <v>1061.552402777778</v>
       </c>
       <c r="D43" s="5">
         <v>980.3099999999999</v>
@@ -3559,13 +3559,13 @@
         <v>897.29</v>
       </c>
       <c r="F43" s="6">
-        <v>1493.002458689371</v>
+        <v>8.287419569093236</v>
       </c>
       <c r="G43" s="6">
-        <v>1640.391891448448</v>
+        <v>18.30650099497129</v>
       </c>
       <c r="H43" s="5">
-        <v>31149.95384722222</v>
+        <v>2040.333847222222</v>
       </c>
       <c r="I43" s="5">
         <v>1960.62</v>
@@ -3574,13 +3574,13 @@
         <v>1678.63</v>
       </c>
       <c r="K43" s="6">
-        <v>1488.780786038203</v>
+        <v>4.065746917925058</v>
       </c>
       <c r="L43" s="6">
-        <v>1755.677180035042</v>
+        <v>21.54756243020928</v>
       </c>
       <c r="M43" s="5">
-        <v>464721.3437777778</v>
+        <v>28077.04377777778</v>
       </c>
       <c r="N43" s="5">
         <v>26422.5</v>
@@ -3589,13 +3589,13 @@
         <v>21636.25</v>
       </c>
       <c r="P43" s="6">
-        <v>1658.809135311866</v>
+        <v>6.261874454642006</v>
       </c>
       <c r="Q43" s="6">
-        <v>2047.883037854424</v>
+        <v>29.76853095050106</v>
       </c>
       <c r="R43" s="5">
-        <v>925894.5444027778</v>
+        <v>52605.94440277779</v>
       </c>
       <c r="S43" s="5">
         <v>52019</v>
@@ -3604,10 +3604,10 @@
         <v>44843.86</v>
       </c>
       <c r="U43" s="6">
-        <v>1679.916077592376</v>
+        <v>1.128326962797812</v>
       </c>
       <c r="V43" s="6">
-        <v>1964.70750823586</v>
+        <v>17.30913530364646</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -3618,7 +3618,7 @@
         <v>99</v>
       </c>
       <c r="C44" s="5">
-        <v>21369.86</v>
+        <v>821.92</v>
       </c>
       <c r="D44" s="5">
         <v>846.78</v>
@@ -3627,13 +3627,13 @@
         <v>824.1799999999999</v>
       </c>
       <c r="F44" s="6">
-        <v>2423.661399655165</v>
+        <v>-2.935827487659134</v>
       </c>
       <c r="G44" s="6">
-        <v>2492.863209493072</v>
+        <v>-0.274211943992816</v>
       </c>
       <c r="H44" s="5">
-        <v>42739.72</v>
+        <v>1643.84</v>
       </c>
       <c r="I44" s="5">
         <v>1693.56</v>
@@ -3642,13 +3642,13 @@
         <v>1648.36</v>
       </c>
       <c r="K44" s="6">
-        <v>2423.661399655165</v>
+        <v>-2.935827487659134</v>
       </c>
       <c r="L44" s="6">
-        <v>2492.863209493072</v>
+        <v>-0.274211943992816</v>
       </c>
       <c r="M44" s="5">
-        <v>641095.8</v>
+        <v>24657.6</v>
       </c>
       <c r="N44" s="5">
         <v>25403.4</v>
@@ -3657,13 +3657,13 @@
         <v>23626.4</v>
       </c>
       <c r="P44" s="6">
-        <v>2423.661399655164</v>
+        <v>-2.935827487659143</v>
       </c>
       <c r="Q44" s="6">
-        <v>2613.472217519385</v>
+        <v>4.364609081366595</v>
       </c>
       <c r="R44" s="5">
-        <v>1282191.6</v>
+        <v>49315.2</v>
       </c>
       <c r="S44" s="5">
         <v>50806.8</v>
@@ -3672,10 +3672,10 @@
         <v>46703.3</v>
       </c>
       <c r="U44" s="6">
-        <v>2423.661399655164</v>
+        <v>-2.935827487659143</v>
       </c>
       <c r="V44" s="6">
-        <v>2645.398290913062</v>
+        <v>5.592538428761981</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -3686,7 +3686,7 @@
         <v>101</v>
       </c>
       <c r="C45" s="5">
-        <v>5107.374888888889</v>
+        <v>518.3348888888888</v>
       </c>
       <c r="D45" s="5">
         <v>410.8</v>
@@ -3695,13 +3695,13 @@
         <v>373.13</v>
       </c>
       <c r="F45" s="6">
-        <v>1143.275289408201</v>
+        <v>26.17694471491938</v>
       </c>
       <c r="G45" s="6">
-        <v>1268.792348213462</v>
+        <v>38.91536164041723</v>
       </c>
       <c r="H45" s="5">
-        <v>10277.36044444444</v>
+        <v>1099.280444444444</v>
       </c>
       <c r="I45" s="5">
         <v>821.6</v>
@@ -3710,13 +3710,13 @@
         <v>1243.98</v>
       </c>
       <c r="K45" s="6">
-        <v>1150.895867142703</v>
+        <v>33.79752244942117</v>
       </c>
       <c r="L45" s="6">
-        <v>726.1676590013059</v>
+        <v>-11.63198407977264</v>
       </c>
       <c r="M45" s="5">
-        <v>151781.2187222222</v>
+        <v>14110.01872222222</v>
       </c>
       <c r="N45" s="5">
         <v>13744.6</v>
@@ -3725,13 +3725,13 @@
         <v>17029.25</v>
       </c>
       <c r="P45" s="6">
-        <v>1004.297096475868</v>
+        <v>2.658634825474897</v>
       </c>
       <c r="Q45" s="6">
-        <v>791.2971429876374</v>
+        <v>-17.14245358884142</v>
       </c>
       <c r="R45" s="5">
-        <v>303109.7822777778</v>
+        <v>27767.38227777778</v>
       </c>
       <c r="S45" s="5">
         <v>27813.02</v>
@@ -3740,10 +3740,10 @@
         <v>31941.83</v>
       </c>
       <c r="U45" s="6">
-        <v>989.8125492225504</v>
+        <v>-0.164087618756343</v>
       </c>
       <c r="V45" s="6">
-        <v>848.9430701928404</v>
+        <v>-13.06890595254632</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -3754,7 +3754,7 @@
         <v>103</v>
       </c>
       <c r="C46" s="5">
-        <v>5627.4</v>
+        <v>216.44</v>
       </c>
       <c r="D46" s="5">
         <v>144.38</v>
@@ -3763,13 +3763,13 @@
         <v>208.58</v>
       </c>
       <c r="F46" s="6">
-        <v>3797.631250865771</v>
+        <v>49.90995982823106</v>
       </c>
       <c r="G46" s="6">
-        <v>2597.957618180074</v>
+        <v>3.768338287467631</v>
       </c>
       <c r="H46" s="5">
-        <v>11254.8</v>
+        <v>432.88</v>
       </c>
       <c r="I46" s="5">
         <v>288.76</v>
@@ -3778,13 +3778,13 @@
         <v>417.16</v>
       </c>
       <c r="K46" s="6">
-        <v>3797.631250865771</v>
+        <v>49.90995982823106</v>
       </c>
       <c r="L46" s="6">
-        <v>2597.957618180074</v>
+        <v>3.768338287467631</v>
       </c>
       <c r="M46" s="5">
-        <v>169044.3828055556</v>
+        <v>6715.582805555556</v>
       </c>
       <c r="N46" s="5">
         <v>4331.4</v>
@@ -3793,13 +3793,13 @@
         <v>8373.530000000001</v>
       </c>
       <c r="P46" s="6">
-        <v>3802.765452406972</v>
+        <v>55.04416136943151</v>
       </c>
       <c r="Q46" s="6">
-        <v>1918.794735381082</v>
+        <v>-19.79985972994</v>
       </c>
       <c r="R46" s="5">
-        <v>337959.7828055556</v>
+        <v>13302.18280555556</v>
       </c>
       <c r="S46" s="5">
         <v>8662.799999999999</v>
@@ -3808,10 +3808,10 @@
         <v>16813.55</v>
       </c>
       <c r="U46" s="6">
-        <v>3801.276524975246</v>
+        <v>53.55523393770556</v>
       </c>
       <c r="V46" s="6">
-        <v>1910.044177497052</v>
+        <v>-20.88415114264652</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -3822,7 +3822,7 @@
         <v>105</v>
       </c>
       <c r="C47" s="5">
-        <v>16223.29</v>
+        <v>623.97</v>
       </c>
       <c r="D47" s="5">
         <v>624.21</v>
@@ -3831,13 +3831,13 @@
         <v>773.0700000000001</v>
       </c>
       <c r="F47" s="6">
-        <v>2499.011550599959</v>
+        <v>-0.03844859902917433</v>
       </c>
       <c r="G47" s="6">
-        <v>1998.553817894887</v>
+        <v>-19.28673988125267</v>
       </c>
       <c r="H47" s="5">
-        <v>32446.58</v>
+        <v>1247.94</v>
       </c>
       <c r="I47" s="5">
         <v>1422.42</v>
@@ -3846,13 +3846,13 @@
         <v>1268.5</v>
       </c>
       <c r="K47" s="6">
-        <v>2181.082943153218</v>
+        <v>-12.26641920107985</v>
       </c>
       <c r="L47" s="6">
-        <v>2457.869925108396</v>
+        <v>-1.620811982656677</v>
       </c>
       <c r="M47" s="5">
-        <v>486698.7</v>
+        <v>18719.1</v>
       </c>
       <c r="N47" s="5">
         <v>20988.3</v>
@@ -3861,13 +3861,13 @@
         <v>21347.72</v>
       </c>
       <c r="P47" s="6">
-        <v>2218.904818398822</v>
+        <v>-10.81173796829663</v>
       </c>
       <c r="Q47" s="6">
-        <v>2179.862673859316</v>
+        <v>-12.31335243295304</v>
       </c>
       <c r="R47" s="5">
-        <v>973397.4</v>
+        <v>37438.2</v>
       </c>
       <c r="S47" s="5">
         <v>40584.6</v>
@@ -3876,10 +3876,10 @@
         <v>40960.32</v>
       </c>
       <c r="U47" s="6">
-        <v>2298.4402950873</v>
+        <v>-7.752694371756778</v>
       </c>
       <c r="V47" s="6">
-        <v>2276.439930156796</v>
+        <v>-8.598858602667173</v>
       </c>
     </row>
     <row r="48" spans="1:22">
@@ -4275,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="R53" s="5">
-        <v>2870.049694444444</v>
+        <v>2870.049694444445</v>
       </c>
       <c r="S53" s="5">
         <v>0</v>
